--- a/data/file_generation/input/data_57/2025-10-16_08_30_巴西甲_桑托斯[16]VS科林蒂安[12]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-16_08_30_巴西甲_桑托斯[16]VS科林蒂安[12]_标盘.xlsx
@@ -49178,26 +49178,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62F2DCA7-176A-4BD9-955E-1896E0BED17E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27B0F4F4-833F-4420-899C-9F4E598C380C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2CBDBAF-61D2-42F5-A86A-556518554495}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A420C4E-EA2B-4BF9-9CDF-228A3D334BCB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2CA79A9-B515-4228-ABED-19C3104B63CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BDA3DC3-D22F-4EB2-B739-68C49073E951}"/>
 </file>